--- a/meta/en/15-2-1.xlsx
+++ b/meta/en/15-2-1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11835"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист 1" sheetId="2" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>1. Indicator information</t>
   </si>
@@ -97,47 +97,55 @@
     <t>15. Protect, restore and promote sustainable use of terrestrial ecosystems, sustainably manage forests, combat desertification, and halt and reverse land degradation and halt biodiversity loss</t>
   </si>
   <si>
-    <t>The data is available to interested parties on the websites of specialized bodies and official statistics, as well as country reports on biodiversity.</t>
-  </si>
-  <si>
     <t>15.2 By 2020, promote the implementation of sustainable management of all types of forests, halt deforestation, restore degraded forests and substantially increase afforestation and reforestation globally</t>
   </si>
   <si>
     <t>15.2.1 Progress towards sustainable forest management</t>
   </si>
   <si>
-    <t>SAEPF, Department of Forest Ecosystem Development, State Institution “</t>
-  </si>
-  <si>
-    <t>+996 (312) 54-88-42,  +996 (312) 54-03-99</t>
-  </si>
-  <si>
-    <t>Kyrgyz Forest Management" Zhumaev Nurlan Kadyrovich, Chukumbaev Sabyr Zholochievich"</t>
-  </si>
-  <si>
-    <t>Reforestation in forests of national importance includes: planting and sowing forests; promoting natural regeneration of forests. 
-Also, measures are being taken to create plantings on ravines, gullies, sands and other inconvenient lands, the cultivation and introduction of young trees into the category of valuable tree plantations in forests of national importance, the creation of nurseries of tree and shrub species, the planting of seedlings and cuttings of tree, shrub, fruit and berry and technical breeds in schools. 
-Increase of forests due to reforestation measures. Changing the forest area will allow us to assess the preservation of natural forest ecosystems. The dynamic growth of the indicator shows an adequate policy in the field of forest conservation and enhancement.</t>
-  </si>
-  <si>
-    <t> The rate of net change in forest area per year;
- Aboveground biomass reserve in forests (t/ha);
- The share of forest areas located in protected areas;
- The proportion of forest areas for which there is a long-term forest management plan;
- Certified forest areas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National forest inventory, accounting of the forest fund </t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-"The SAEPF generates data on the area of reforestation in forests of national importance, including planting and sowing forests, and promoting natural regeneration. 
-The SAEPF collects data based on reports from forestry enterprises, nature parks, and nature reserves by region and summarizes information at the republic level. 
-The NSC collects information from forestry enterprises and other enterprises engaged in forestry work based on the state statistical reporting form "Forestry Work Report".
-The data of the National Forest Inventory of the Kyrgyz Republic were approved by Resolution No. 407 of the Government of the Kyrgyz Republic dated July 26, 11. The second national forest inventory of the Kyrgyz Republic has been launched."</t>
-  </si>
-  <si>
-    <t>The National SDG Reporting Platform of the Kyrgyz Republic: https://sustainabledevelopment-kyrgyzstan .github.io</t>
+    <t>Forest Service (Interregional Department for Forest and Game Management under the Ministry of Emergency Situations of the Kyrgyz Republic)</t>
+  </si>
+  <si>
+    <t>Mirbek Bekbosunovich Kadyrov</t>
+  </si>
+  <si>
+    <t>Tel.: +996 700 393 844, 59-01-56</t>
+  </si>
+  <si>
+    <t>e-mail: ulou@forest.gov.kg</t>
+  </si>
+  <si>
+    <t>тел. 59-01-56, e-mail: ulou@forest.gov.kg</t>
+  </si>
+  <si>
+    <t>The 2023 Forest Fund Inventory was conducted in accordance with the unified procedure for maintaining forest fund records, approved by Resolution of the Government of the Kyrgyz Republic No. 111 of 11 March 2015.</t>
+  </si>
+  <si>
+    <t>The Forest Fund Inventory is one of the activities within the forest accounting system and is carried out periodically every five years for the one-time determination of the quantitative and qualitative characteristics of the forest fund and the changes occurring therein.</t>
+  </si>
+  <si>
+    <t>The present Forest Fund Inventory, as well as previous inventories, was conducted using Form No. 1 “Distribution of areas of the State Forest Fund or specially protected natural areas by land categories” and Form No. 2 “Distribution of forest area and timber stock by dominant species and age groups”.</t>
+  </si>
+  <si>
+    <t>The sources of the Inventory are primary documentation of forestry enterprises, nature reserves and natural parks, forest management materials, the National Forest Inventory, and materials of the Department for Forest Ecosystem Development and Strategic Planning.</t>
+  </si>
+  <si>
+    <t>Training seminars were conducted on the preparation of materials for the 2023 Forest Fund Inventory for all forestry enterprises, nature reserves and natural parks of the Kyrgyz Republic; their reports were received, a database was established, and an analysis of forest conditions and forest management practices was carried out at the level of forestry enterprises, natural parks and nature reserves, with aggregated data at the oblast level.</t>
+  </si>
+  <si>
+    <t>The assessment of forest condition and the activities of forest entities was carried out based on 12 criteria, including changes in lands of the State Forest Fund and specially protected natural areas, as well as outside the territories of the State Forest Fund and specially protected natural areas during the inter-inventory period; species composition; age structure; growing stock and increment; establishment of forest plantations; condition of forest plantations; nursery management; conversion to forest-covered land; forest fellings; illegal logging; forest types; and forest use.</t>
+  </si>
+  <si>
+    <t>ulou@forest.gov.kg</t>
+  </si>
+  <si>
+    <t>Compliant.</t>
+  </si>
+  <si>
+    <t>Data are available.</t>
+  </si>
+  <si>
+    <t>By territory.</t>
   </si>
 </sst>
 </file>
@@ -258,7 +266,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -300,6 +308,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -634,7 +645,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -642,7 +653,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -656,7 +667,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -664,27 +675,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="12"/>
+      <c r="B8" s="13" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="9" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="8"/>
+      <c r="B9" s="12" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="10" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>31</v>
+      <c r="B10" s="8" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -698,21 +713,23 @@
         <v>11</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="10"/>
+      <c r="B13" s="10" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="14" spans="1:2" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -726,7 +743,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="153.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -734,7 +751,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -747,7 +764,9 @@
       <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="6"/>
+      <c r="B19" s="6" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="20" spans="1:2" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
@@ -772,27 +791,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="5"/>
+      <c r="B24" s="5" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="25" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="9"/>
+      <c r="B25" s="9" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="26" spans="1:2" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
